--- a/reports/misclassified_examples.xlsx
+++ b/reports/misclassified_examples.xlsx
@@ -453,11 +453,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.59815764427185</v>
+        <v>64.19736742973328</v>
       </c>
     </row>
     <row r="3">
@@ -468,11 +468,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32.61099755764008</v>
+        <v>13.96637558937073</v>
       </c>
     </row>
     <row r="4">
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>751</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.05056810379028</v>
+        <v>58.87399315834045</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.71684813499451</v>
+        <v>77.21412181854248</v>
       </c>
     </row>
     <row r="6">
@@ -513,197 +513,197 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82.41174221038818</v>
+        <v>68.13728213310242</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42.11599826812744</v>
+        <v>68.90195608139038</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>83.97315144538879</v>
+        <v>28.2518208026886</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>619</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41.92216992378235</v>
+        <v>47.04465270042419</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>57.32553005218506</v>
+        <v>25.0228077173233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9.55231711268425</v>
+        <v>36.39848232269287</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>619</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.94764828681946</v>
+        <v>88.47380876541138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36.55439615249634</v>
+        <v>48.9942193031311</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33.53778719902039</v>
+        <v>21.76368534564972</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>75.71475505828857</v>
+        <v>27.9911071062088</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>672</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.48088973760605</v>
+        <v>55.18952608108521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45.37264406681061</v>
+        <v>24.08448606729507</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.84650534391403</v>
+        <v>39.07727599143982</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>44.37278211116791</v>
+        <v>31.56734108924866</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>485</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.443443775177</v>
+        <v>77.05467939376831</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -742,457 +742,457 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>46.4042991399765</v>
+        <v>47.48498499393463</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>578</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>39.61619138717651</v>
+        <v>13.23206126689911</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>672</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.32729768753052</v>
+        <v>20.53340226411819</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.20600968599319</v>
+        <v>61.51724457740784</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>686</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>35.03953516483307</v>
+        <v>20.44901847839355</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>678</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>76.04163289070129</v>
+        <v>30.39757013320923</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>696</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.88333892822266</v>
+        <v>26.37360990047455</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.59943985939026</v>
+        <v>76.82222723960876</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>678</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>34.03441309928894</v>
+        <v>29.31213080883026</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>34.26091969013214</v>
+        <v>56.57117962837219</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>674</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.78491812944412</v>
+        <v>74.53105449676514</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>672</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>28.04143130779266</v>
+        <v>15.37603586912155</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>616</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>35.23972034454346</v>
+        <v>17.81049966812134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>546</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>23.70217740535736</v>
+        <v>35.39836406707764</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>56.42753839492798</v>
+        <v>40.49009382724762</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>55.93897104263306</v>
+        <v>18.61212849617004</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>747</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>24.66481477022171</v>
+        <v>9.190170466899872</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>652</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>30.58238327503204</v>
+        <v>37.45478391647339</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>396</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34.78360176086426</v>
+        <v>42.06331968307495</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>162</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>76.2717068195343</v>
+        <v>31.15519881248474</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>546</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38.26124668121338</v>
+        <v>25.54924190044403</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>738</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>82.59203433990479</v>
+        <v>82.65841007232666</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>191</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>19.69188004732132</v>
+        <v>25.36539435386658</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9.927107393741608</v>
+        <v>17.31969863176346</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>63.5528028011322</v>
+        <v>19.81355100870132</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="C46" t="n">
-        <v>30.04558682441711</v>
+        <v>24.11557286977768</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>457</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7.699909806251526</v>
+        <v>33.37239027023315</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>441</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>39.08156454563141</v>
+        <v>19.16993707418442</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>546</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>25.53392350673676</v>
+        <v>13.68414461612701</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>15.08724838495255</v>
+        <v>57.52120614051819</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>672</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>55.77302575111389</v>
+        <v>86.87422275543213</v>
       </c>
     </row>
   </sheetData>
